--- a/data/gated_research/model_ledgers/npb-tie-aware-elo.xlsx
+++ b/data/gated_research/model_ledgers/npb-tie-aware-elo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$3</definedName>
@@ -844,14 +844,26 @@
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>1.0246</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:32.169357Z</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr"/>
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr"/>
